--- a/docs/Backlog.xlsx
+++ b/docs/Backlog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niceonline-my.sharepoint.com/personal/dinesh_wadhwani_nice_com/Documents/Documents/Documents/Personal/TS/Git/coaching-studio/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niceonline-my.sharepoint.com/personal/dinesh_wadhwani_nice_com/Documents/Documents/Documents/Personal/TS/Git/StudioVerse/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{1E020052-0DBA-F345-A8D7-20FAEAB55367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92350098-6588-D44E-8729-47EF64B98E3F}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{1E020052-0DBA-F345-A8D7-20FAEAB55367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6C68306-DAB1-CA43-B20A-FCB1D4ADD4A6}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{D2DD8507-5C6E-3A49-9817-3141F40E6022}"/>
+    <workbookView xWindow="1700" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{D2DD8507-5C6E-3A49-9817-3141F40E6022}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3260,12 +3260,12 @@
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3435,22 +3435,22 @@
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="4" t="s">
         <v>67</v>
       </c>
     </row>
